--- a/sheet-template/plato-content-template.xlsx
+++ b/sheet-template/plato-content-template.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -660,7 +660,8 @@
     <col width="28" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -741,6 +742,11 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>published</t>
         </is>
       </c>
@@ -813,7 +819,8 @@
       </c>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -891,7 +898,8 @@
           <t>Team Placeholder</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>

--- a/sheet-template/plato-content-template.xlsx
+++ b/sheet-template/plato-content-template.xlsx
@@ -57,12 +57,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -642,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -660,8 +661,9 @@
     <col width="28" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -742,10 +744,15 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>image</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>published</t>
         </is>
@@ -819,8 +826,13 @@
       </c>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -898,8 +910,13 @@
           <t>Team Placeholder</t>
         </is>
       </c>
-      <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>solo</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>

--- a/sheet-template/plato-content-template.xlsx
+++ b/sheet-template/plato-content-template.xlsx
@@ -514,12 +514,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ليلة مجتمع إيليت</t>
+          <t>ليلة مجتمع Plato | بالعربية</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Elite community night</t>
+          <t>Plato AR community night</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
